--- a/data/MyTutoringHub_Curriculum_Database.xlsx
+++ b/data/MyTutoringHub_Curriculum_Database.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curriculum Database" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Curriculum Database" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Curriculum Database'!$A$1:$E$1212</definedName>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1212"/>
+  <dimension ref="A1:E1513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -33161,6 +33161,8133 @@
         </is>
       </c>
     </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>Leaving Certificate (SEC)</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>Leaving Certificate</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>Leaving Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>Leaving Certificate (SEC)</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>Leaving Certificate</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>Leaving Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>Leaving Certificate (SEC)</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>Leaving Certificate</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>Leaving Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>Leaving Certificate (SEC)</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>Leaving Certificate</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>Leaving Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>Leaving Certificate (SEC)</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>Leaving Certificate</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>Leaving Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>Leaving Certificate (SEC)</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>Leaving Certificate</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>Leaving Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>Leaving Certificate (SEC)</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>Leaving Certificate</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>Leaving Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>Leaving Certificate (SEC)</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>Leaving Certificate</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>Leaving Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>Leaving Certificate (SEC)</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>Leaving Certificate</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>Leaving Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>Leaving Certificate (SEC)</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>Leaving Certificate</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>Leaving Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>Junior Certificate (SEC)</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>Junior Certificate</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>Junior Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>Junior Certificate (SEC)</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>Junior Certificate</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>Junior Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>Junior Certificate (SEC)</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>Junior Certificate</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>Junior Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>WAEC</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>SSCE</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>West African Senior School Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>WAEC</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>SSCE</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>West African Senior School Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>WAEC</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>SSCE</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>West African Senior School Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>WAEC</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>SSCE</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>West African Senior School Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>WAEC</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>SSCE</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>West African Senior School Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>WAEC</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>SSCE</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>West African Senior School Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>WAEC</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>SSCE</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>West African Senior School Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>WAEC</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>SSCE</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>West African Senior School Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>WAEC</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>SSCE</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>West African Senior School Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>NECO</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>SSCE</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>National Examinations Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>NECO</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>SSCE</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>National Examinations Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>NECO</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>SSCE</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>National Examinations Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>NECO</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>SSCE</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>National Examinations Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>NECO</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>SSCE</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>National Examinations Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>WAEC Ghana</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>WASSCE</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>West African Senior School Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>WAEC Ghana</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>WASSCE</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>West African Senior School Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>WAEC Ghana</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>WASSCE</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>West African Senior School Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>WAEC Ghana</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>WASSCE</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>West African Senior School Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>WAEC Ghana</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>WASSCE</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>West African Senior School Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>WAEC Ghana</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>WASSCE</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>West African Senior School Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>Sri Lanka DOE</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>GCE Advanced Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>Sri Lanka DOE</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>GCE Advanced Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>Sri Lanka DOE</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>GCE Advanced Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>Sri Lanka DOE</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>GCE Advanced Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>Sri Lanka DOE</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>GCE Advanced Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>Sri Lanka DOE</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>O Level</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>GCE Ordinary Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>Sri Lanka DOE</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>O Level</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>GCE Ordinary Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>Sri Lanka DOE</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>O Level</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>GCE Ordinary Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>Cambridge A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>Cambridge A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>Cambridge A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>Grade 11-12</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>National Examination Board</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>Grade 11-12</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>National Examination Board</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>Grade 11-12</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>National Examination Board</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>Grade 11-12</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>National Examination Board</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>Grade 11-12</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>National Examination Board</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>Grade 11-12</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>National Examination Board</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>Cambridge A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>Cambridge A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>Bangladesh Education Board</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>HSC</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>Higher Secondary Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>Bangladesh Education Board</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>HSC</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>Higher Secondary Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>Bangladesh Education Board</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>HSC</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>Higher Secondary Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>Bangladesh Education Board</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>HSC</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>Higher Secondary Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>Bangladesh Education Board</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>HSC</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>Higher Secondary Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>Bangladesh Education Board</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>SSC</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>Secondary School Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>Bangladesh Education Board</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>SSC</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>Secondary School Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>Cambridge A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>KNEC</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>KCSE</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>Kenya Certificate of Secondary Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>KNEC</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>KCSE</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>Kenya Certificate of Secondary Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>KNEC</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>KCSE</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>Kenya Certificate of Secondary Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>KNEC</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>KCSE</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>Kenya Certificate of Secondary Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>KNEC</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>KCSE</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>Kenya Certificate of Secondary Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>KNEC</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>KCSE</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>Kenya Certificate of Secondary Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>Cambridge A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>NECTA</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>ACSEE</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>Advanced Certificate of Secondary Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>NECTA</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>ACSEE</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>Advanced Certificate of Secondary Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>NECTA</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>ACSEE</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>Advanced Certificate of Secondary Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>NECTA</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>ACSEE</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>Advanced Certificate of Secondary Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>NECTA</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>CSEE</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>Certificate of Secondary Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>NECTA</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>CSEE</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>Certificate of Secondary Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>ZIMSEC</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>Zimbabwe School Examinations Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>ZIMSEC</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>Zimbabwe School Examinations Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>ZIMSEC</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>Zimbabwe School Examinations Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>ZIMSEC</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>Zimbabwe School Examinations Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>ZIMSEC</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>O Level</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>Zimbabwe School Examinations Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>ZIMSEC</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>O Level</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>Zimbabwe School Examinations Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>Cambridge A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>CAPE / CSEC</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>CAPE</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>Caribbean Advanced Proficiency Examination</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>CAPE / CSEC</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>CAPE</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>Caribbean Advanced Proficiency Examination</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>CAPE / CSEC</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>CAPE</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>Caribbean Advanced Proficiency Examination</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>CAPE / CSEC</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>CAPE</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>Caribbean Advanced Proficiency Examination</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>CAPE / CSEC</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>CSEC</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>Caribbean Secondary Education Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>CAPE / CSEC</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>CSEC</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>Caribbean Secondary Education Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>CAPE / CSEC</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>CSEC</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>Caribbean Secondary Education Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>CAPE / CSEC</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>CAPE</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>Caribbean Advanced Proficiency Examination</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>CAPE / CSEC</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>CAPE</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>Caribbean Advanced Proficiency Examination</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>CAPE / CSEC</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>CSEC</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>Caribbean Secondary Education Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>CAPE / CSEC</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>CSEC</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>Caribbean Secondary Education Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>Barbados</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>CAPE / CSEC</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>CAPE</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>Caribbean Advanced Proficiency Examination</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>Barbados</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>CAPE / CSEC</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>CSEC</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>Caribbean Secondary Education Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>Alberta Diploma Exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>Alberta Diploma Exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>Alberta Diploma Exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>Alberta Diploma Exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>Alberta Diploma Exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>BC Provincial Exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>BC Provincial Exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>BC Provincial Exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>BC Provincial Exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>BC Provincial Exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>Ontario Secondary School</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>Ontario Secondary School</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>Ontario Secondary School</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>Ontario Secondary School</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>Ontario Secondary School</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>Manitoba Senior 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>Manitoba Senior 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>Manitoba Senior 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>Manitoba Senior 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>Saskatchewan Grade 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>Saskatchewan Grade 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>Saskatchewan Grade 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>Nova Scotia</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>Nova Scotia Grade 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>Nova Scotia</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>Nova Scotia Grade 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>Nova Scotia</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>Nova Scotia Grade 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>Quebec</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>Pre-University</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>CEGEP / DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>Quebec</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>Pre-University</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>CEGEP / DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>Quebec</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>Pre-University</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>CEGEP / DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>Quebec</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>Pre-University</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>CEGEP / DEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>Calculus AB</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>Advanced Placement</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>Advanced Placement</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>Advanced Placement</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>Advanced Placement</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>IB</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>IB Diploma Programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>IB</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>IB Diploma Programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>IB</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>IB Diploma Programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>Cambridge A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>Singapore-Cambridge A Level</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>Further Mathematics</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>Singapore-Cambridge GCE A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>Singapore-Cambridge A Level</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>Singapore-Cambridge GCE A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>Singapore-Cambridge A Level</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>Singapore-Cambridge GCE A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>Singapore-Cambridge A Level</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>Singapore-Cambridge GCE A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>Singapore-Cambridge A Level</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>Singapore-Cambridge GCE A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>Singapore-Cambridge O Level</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>O Level</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>Singapore-Cambridge GCE O Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>Singapore-Cambridge O Level</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>O Level</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>Singapore-Cambridge GCE O Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>Singapore-Cambridge O Level</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>O Level</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>Singapore-Cambridge GCE O Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>Singapore-Cambridge O Level</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>O Level</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>Singapore-Cambridge GCE O Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>Singapore-Cambridge O Level</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>O Level</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>Singapore-Cambridge GCE O Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>IB</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>IB Diploma Programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>IB</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>IB Diploma Programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>German</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>Gymnasium</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>Gymnasium Abitur</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>Gymnasium</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>Abitur</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>Gymnasium Abitur</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>German National / State Curriculum</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>Grade 10-12</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>German National Curriculum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>IB</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>IB Diploma Programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>Cambridge A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>French Baccalauréat</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>Baccalauréat</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>Baccalauréat Général</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>French Baccalauréat</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>Baccalauréat</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>Baccalauréat Général</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>French Baccalauréat</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>Baccalauréat</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>Baccalauréat Général</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>French Baccalauréat</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>Baccalauréat</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>Baccalauréat Général</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>French Baccalauréat</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>Baccalauréat</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="E1371" t="inlineStr">
+        <is>
+          <t>Baccalauréat Général</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>French Baccalauréat</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>Baccalauréat</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1372" t="inlineStr">
+        <is>
+          <t>Baccalauréat Général</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>French Baccalauréat</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>Baccalauréat</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+      <c r="E1373" t="inlineStr">
+        <is>
+          <t>Baccalauréat Général</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>IB</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>IB Diploma Programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>Cambridge A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>HKDSE</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>DSE</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>Further Mathematics</t>
+        </is>
+      </c>
+      <c r="E1376" t="inlineStr">
+        <is>
+          <t>HKDSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>HKDSE</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>DSE</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>HKDSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>HKDSE</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>DSE</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>HKDSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>HKDSE</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>DSE</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>HKDSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>HKDSE</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>DSE</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>HKDSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>HKDSE</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>DSE</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="E1381" t="inlineStr">
+        <is>
+          <t>HKDSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>HKDSE</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>DSE</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1382" t="inlineStr">
+        <is>
+          <t>HKDSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>Hong Kong Curriculum</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>Chinese</t>
+        </is>
+      </c>
+      <c r="E1383" t="inlineStr">
+        <is>
+          <t>Hong Kong Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>Hong Kong Curriculum</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>General Studies</t>
+        </is>
+      </c>
+      <c r="E1384" t="inlineStr">
+        <is>
+          <t>Hong Kong Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>IB</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1385" t="inlineStr">
+        <is>
+          <t>IB Diploma Programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>Japanese University Entrance</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1386" t="inlineStr">
+        <is>
+          <t>Daigaku Nyushi Kyotsu Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>Japanese University Entrance</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1387" t="inlineStr">
+        <is>
+          <t>Daigaku Nyushi Kyotsu Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>Japanese University Entrance</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>Daigaku Nyushi Kyotsu Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>Japanese University Entrance</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>Daigaku Nyushi Kyotsu Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>Japanese University Entrance</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1390" t="inlineStr">
+        <is>
+          <t>Daigaku Nyushi Kyotsu Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>IB</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>IB Diploma Programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>Cambridge A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>CSAT (Suneung)</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>College Scholastic Ability Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>CSAT (Suneung)</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>College Scholastic Ability Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>CSAT (Suneung)</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>College Scholastic Ability Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>CSAT (Suneung)</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>College Scholastic Ability Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>CSAT (Suneung)</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>College Scholastic Ability Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>IB</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>IB Diploma Programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>YKS (Turkish University Entrance)</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1399" t="inlineStr">
+        <is>
+          <t>Yükseköğretim Kurumları Sınavı</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>YKS (Turkish University Entrance)</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1400" t="inlineStr">
+        <is>
+          <t>Yükseköğretim Kurumları Sınavı</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>YKS (Turkish University Entrance)</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1401" t="inlineStr">
+        <is>
+          <t>Yükseköğretim Kurumları Sınavı</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>YKS (Turkish University Entrance)</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1402" t="inlineStr">
+        <is>
+          <t>Yükseköğretim Kurumları Sınavı</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>IB</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1403" t="inlineStr">
+        <is>
+          <t>IB Diploma Programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1404" t="inlineStr">
+        <is>
+          <t>Cambridge A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>ENEM</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>Exame Nacional do Ensino Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>ENEM</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1406" t="inlineStr">
+        <is>
+          <t>Exame Nacional do Ensino Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>ENEM</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1407" t="inlineStr">
+        <is>
+          <t>Exame Nacional do Ensino Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>ENEM</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1408" t="inlineStr">
+        <is>
+          <t>Exame Nacional do Ensino Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>IB</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1409" t="inlineStr">
+        <is>
+          <t>IB Diploma Programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>UN (Indonesian National Exam)</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1410" t="inlineStr">
+        <is>
+          <t>Ujian Nasional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>UN (Indonesian National Exam)</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1411" t="inlineStr">
+        <is>
+          <t>Ujian Nasional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>UN (Indonesian National Exam)</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1412" t="inlineStr">
+        <is>
+          <t>Ujian Nasional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>UN (Indonesian National Exam)</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1413" t="inlineStr">
+        <is>
+          <t>Ujian Nasional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1414" t="inlineStr">
+        <is>
+          <t>Cambridge A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>IB</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1415" t="inlineStr">
+        <is>
+          <t>IB Diploma Programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>Thai GAT/PAT</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1416" t="inlineStr">
+        <is>
+          <t>Thai University Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>Thai GAT/PAT</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1417" t="inlineStr">
+        <is>
+          <t>Thai University Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>Thai GAT/PAT</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1418" t="inlineStr">
+        <is>
+          <t>Thai University Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1419" t="inlineStr">
+        <is>
+          <t>Cambridge A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>IB</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1420" t="inlineStr">
+        <is>
+          <t>IB Diploma Programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>DepEd K-12 / PEPT</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>Senior High</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1421" t="inlineStr">
+        <is>
+          <t>Philippine Senior High School</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>DepEd K-12 / PEPT</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>Senior High</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1422" t="inlineStr">
+        <is>
+          <t>Philippine Senior High School</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>DepEd K-12 / PEPT</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>Senior High</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1423" t="inlineStr">
+        <is>
+          <t>Philippine Senior High School</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>DepEd K-12 / PEPT</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>Senior High</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1424" t="inlineStr">
+        <is>
+          <t>Philippine Senior High School</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1425" t="inlineStr">
+        <is>
+          <t>Cambridge A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>Myanmar</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>Myanmar Basic Education</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>Grade 11</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1426" t="inlineStr">
+        <is>
+          <t>Myanmar Matriculation Exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>Myanmar</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>Myanmar Basic Education</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>Grade 11</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1427" t="inlineStr">
+        <is>
+          <t>Myanmar Matriculation Exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>Myanmar</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>Myanmar Basic Education</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>Grade 11</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1428" t="inlineStr">
+        <is>
+          <t>Myanmar Matriculation Exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>Myanmar</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>Myanmar Basic Education</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>Grade 11</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1429" t="inlineStr">
+        <is>
+          <t>Myanmar Matriculation Exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>Ethiopia</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>Ethiopian Education Board</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1430" t="inlineStr">
+        <is>
+          <t>Ethiopian University Entrance Exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>Ethiopia</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>Ethiopian Education Board</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1431" t="inlineStr">
+        <is>
+          <t>Ethiopian University Entrance Exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>Ethiopia</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>Ethiopian Education Board</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1432" t="inlineStr">
+        <is>
+          <t>Ethiopian University Entrance Exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>Ethiopia</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>Ethiopian Education Board</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1433" t="inlineStr">
+        <is>
+          <t>Ethiopian University Entrance Exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>Egyptian Thanaweya Amma</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1434" t="inlineStr">
+        <is>
+          <t>Thanaweya Amma</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>Egyptian Thanaweya Amma</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1435" t="inlineStr">
+        <is>
+          <t>Thanaweya Amma</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>Egyptian Thanaweya Amma</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1436" t="inlineStr">
+        <is>
+          <t>Thanaweya Amma</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>Egyptian Thanaweya Amma</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1437" t="inlineStr">
+        <is>
+          <t>Thanaweya Amma</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1438" t="inlineStr">
+        <is>
+          <t>Cambridge A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>IB</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1439" t="inlineStr">
+        <is>
+          <t>IB Diploma Programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>Jordanian Tawjihi</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1440" t="inlineStr">
+        <is>
+          <t>General Secondary Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>Jordanian Tawjihi</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1441" t="inlineStr">
+        <is>
+          <t>General Secondary Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>Jordanian Tawjihi</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1442" t="inlineStr">
+        <is>
+          <t>General Secondary Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>Jordanian Tawjihi</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1443" t="inlineStr">
+        <is>
+          <t>General Secondary Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1444" t="inlineStr">
+        <is>
+          <t>Cambridge A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>Oman MoE</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1445" t="inlineStr">
+        <is>
+          <t>Oman General Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>Oman MoE</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1446" t="inlineStr">
+        <is>
+          <t>Oman General Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>Oman MoE</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1447" t="inlineStr">
+        <is>
+          <t>Oman General Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1448" t="inlineStr">
+        <is>
+          <t>Cambridge A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>IGCSE</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1449" t="inlineStr">
+        <is>
+          <t>Cambridge IGCSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>Bahrain MoE</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1450" t="inlineStr">
+        <is>
+          <t>Bahrain Secondary Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>Bahrain MoE</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1451" t="inlineStr">
+        <is>
+          <t>Bahrain Secondary Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1452" t="inlineStr">
+        <is>
+          <t>Cambridge A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>IGCSE</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1453" t="inlineStr">
+        <is>
+          <t>Cambridge IGCSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>Kuwait MoE</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1454" t="inlineStr">
+        <is>
+          <t>Kuwait Secondary Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>Kuwait MoE</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1455" t="inlineStr">
+        <is>
+          <t>Kuwait Secondary Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1456" t="inlineStr">
+        <is>
+          <t>Cambridge A Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>Cambridge International</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>IGCSE</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1457" t="inlineStr">
+        <is>
+          <t>Cambridge IGCSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>South Australia SACE</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>Years 11–12</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1458" t="inlineStr">
+        <is>
+          <t>South Australian Certificate of Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>South Australia SACE</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>Years 11–12</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1459" t="inlineStr">
+        <is>
+          <t>South Australian Certificate of Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>South Australia SACE</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>Years 11–12</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1460" t="inlineStr">
+        <is>
+          <t>South Australian Certificate of Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>South Australia SACE</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>Years 11–12</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="E1461" t="inlineStr">
+        <is>
+          <t>South Australian Certificate of Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>Western Australia WACE</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>Years 11–12</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1462" t="inlineStr">
+        <is>
+          <t>Western Australian Certificate of Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>Western Australia WACE</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>Years 11–12</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1463" t="inlineStr">
+        <is>
+          <t>Western Australian Certificate of Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>Western Australia WACE</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>Years 11–12</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1464" t="inlineStr">
+        <is>
+          <t>Western Australian Certificate of Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>Tasmania TCE</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>Years 11–12</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1465" t="inlineStr">
+        <is>
+          <t>Tasmanian Certificate of Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>Tasmania TCE</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>Years 11–12</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1466" t="inlineStr">
+        <is>
+          <t>Tasmanian Certificate of Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>Tasmania TCE</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>Years 11–12</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1467" t="inlineStr">
+        <is>
+          <t>Tasmanian Certificate of Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>Australian Curriculum</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>P–12</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1468" t="inlineStr">
+        <is>
+          <t>Australian Curriculum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>Australian Curriculum</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>P–12</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="E1469" t="inlineStr">
+        <is>
+          <t>Australian Curriculum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>Australian Curriculum</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>P–12</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1470" t="inlineStr">
+        <is>
+          <t>Australian Curriculum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>Australian Curriculum</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>P–12</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1471" t="inlineStr">
+        <is>
+          <t>Australian Curriculum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>Australian Curriculum</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>P–12</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1472" t="inlineStr">
+        <is>
+          <t>Australian Curriculum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>University of London International Programmes</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1473" t="inlineStr">
+        <is>
+          <t>UoL International Examination</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>University of London International Programmes</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="E1474" t="inlineStr">
+        <is>
+          <t>UoL International Examination</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>University of London International Programmes</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>Law</t>
+        </is>
+      </c>
+      <c r="E1475" t="inlineStr">
+        <is>
+          <t>UoL International Examination</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>Open University</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1476" t="inlineStr">
+        <is>
+          <t>Open University</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>Open University</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1477" t="inlineStr">
+        <is>
+          <t>Open University</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>Open University</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1478" t="inlineStr">
+        <is>
+          <t>Open University</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>College Board</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>Calculus AB</t>
+        </is>
+      </c>
+      <c r="E1479" t="inlineStr">
+        <is>
+          <t>Advanced Placement</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>College Board</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>Calculus BC</t>
+        </is>
+      </c>
+      <c r="E1480" t="inlineStr">
+        <is>
+          <t>Advanced Placement</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>College Board</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1481" t="inlineStr">
+        <is>
+          <t>Advanced Placement</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>College Board</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1482" t="inlineStr">
+        <is>
+          <t>Scholastic Assessment Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>College Board</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>Reading and Writing</t>
+        </is>
+      </c>
+      <c r="E1483" t="inlineStr">
+        <is>
+          <t>Scholastic Assessment Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>IIT JEE Main</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>Entrance</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1484" t="inlineStr">
+        <is>
+          <t>Joint Entrance Examination Main</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>IIT JEE Main</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>Entrance</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1485" t="inlineStr">
+        <is>
+          <t>Joint Entrance Examination Main</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>IIT JEE Main</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>Entrance</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1486" t="inlineStr">
+        <is>
+          <t>Joint Entrance Examination Main</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>NEET UG</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>Entrance</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1487" t="inlineStr">
+        <is>
+          <t>National Eligibility cum Entrance Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>NEET UG</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>Entrance</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1488" t="inlineStr">
+        <is>
+          <t>National Eligibility cum Entrance Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>NEET UG</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>Entrance</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1489" t="inlineStr">
+        <is>
+          <t>National Eligibility cum Entrance Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>MDCAT</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>Entrance</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1490" t="inlineStr">
+        <is>
+          <t>Medical College Admission Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>MDCAT</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>Entrance</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1491" t="inlineStr">
+        <is>
+          <t>Medical College Admission Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>MDCAT</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>Entrance</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1492" t="inlineStr">
+        <is>
+          <t>Medical College Admission Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>ECAT</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>Entrance</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1493" t="inlineStr">
+        <is>
+          <t>Engineering College Admission Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>ECAT</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>Entrance</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1494" t="inlineStr">
+        <is>
+          <t>Engineering College Admission Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>ECAT</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>Entrance</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1495" t="inlineStr">
+        <is>
+          <t>Engineering College Admission Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>ATAR / Universities</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>Year 12</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1496" t="inlineStr">
+        <is>
+          <t>Australian Tertiary Admission Rank</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>ATAR / Universities</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>Year 12</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1497" t="inlineStr">
+        <is>
+          <t>Australian Tertiary Admission Rank</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>ATAR / Universities</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>Year 12</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1498" t="inlineStr">
+        <is>
+          <t>Australian Tertiary Admission Rank</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>Singapore Universities</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1499" t="inlineStr">
+        <is>
+          <t>Singapore University Admission</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>Singapore Universities</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>A Level</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1500" t="inlineStr">
+        <is>
+          <t>Singapore University Admission</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>Hong Kong Universities</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>DSE</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1501" t="inlineStr">
+        <is>
+          <t>Hong Kong University Admission</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>Hong Kong Universities</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>DSE</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1502" t="inlineStr">
+        <is>
+          <t>Hong Kong University Admission</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>South African Universities</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>Matric</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1503" t="inlineStr">
+        <is>
+          <t>NSC Matric University Admission</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>South African Universities</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>Matric</t>
+        </is>
+      </c>
+      <c r="D1504" t="inlineStr">
+        <is>
+          <t>Physical Sciences</t>
+        </is>
+      </c>
+      <c r="E1504" t="inlineStr">
+        <is>
+          <t>NSC Matric University Admission</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>Nigerian Universities</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>UTME</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1505" t="inlineStr">
+        <is>
+          <t>Unified Tertiary Matriculation Examination</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>Nigerian Universities</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>UTME</t>
+        </is>
+      </c>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1506" t="inlineStr">
+        <is>
+          <t>Unified Tertiary Matriculation Examination</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>Nigerian Universities</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>UTME</t>
+        </is>
+      </c>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1507" t="inlineStr">
+        <is>
+          <t>Unified Tertiary Matriculation Examination</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>Kenyan Universities</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>KCSE</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1508" t="inlineStr">
+        <is>
+          <t>Kenya University Admission</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>Kenyan Universities</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>KCSE</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="E1509" t="inlineStr">
+        <is>
+          <t>Kenya University Admission</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>Egyptian Universities</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>Thanaweya Amma</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1510" t="inlineStr">
+        <is>
+          <t>Egyptian University Admission</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>Egyptian Universities</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>Thanaweya Amma</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E1511" t="inlineStr">
+        <is>
+          <t>Egyptian University Admission</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>Malaysian Universities</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>STPM</t>
+        </is>
+      </c>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E1512" t="inlineStr">
+        <is>
+          <t>Malaysian University Admission</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>Malaysian Universities</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>STPM</t>
+        </is>
+      </c>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E1513" t="inlineStr">
+        <is>
+          <t>Malaysian University Admission</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1212"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
